--- a/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDD2EE4-AE73-4506-A97D-5789ACD7D4E4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE5DF6B-266F-4C2F-B794-383A5A113D5C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="4" r:id="rId1"/>
-    <sheet name="PE, FEBRUARY" sheetId="6" r:id="rId2"/>
+    <sheet name="PE, MARCH" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'PE, FEBRUARY'!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'PE, MARCH'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="77">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>MARCH 2026</t>
+  </si>
+  <si>
+    <t>03/16/2026</t>
   </si>
 </sst>
 </file>
@@ -2339,7 +2342,9 @@
       <c r="B7" s="23">
         <v>1</v>
       </c>
-      <c r="C7" s="19"/>
+      <c r="C7" s="19" t="s">
+        <v>76</v>
+      </c>
       <c r="D7" s="20" t="s">
         <v>68</v>
       </c>
@@ -2347,22 +2352,27 @@
       <c r="F7" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="20"/>
+      <c r="G7" s="20">
+        <v>518463754</v>
+      </c>
       <c r="H7" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I7" s="21"/>
+      <c r="I7" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K7" s="21">
         <f>M7*12</f>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L7" s="27">
         <f>I7-K7</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M7" s="33">
         <f>I7/112</f>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
       <c r="N7" s="26"/>
       <c r="O7" s="26"/>
@@ -3095,19 +3105,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE5DF6B-266F-4C2F-B794-383A5A113D5C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89279520-0F79-4DED-9C38-BA1C6B391C33}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="78">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>03/16/2026</t>
+  </si>
+  <si>
+    <t>03/17/2026</t>
   </si>
 </sst>
 </file>
@@ -2386,7 +2389,9 @@
         <f>B7+1</f>
         <v>2</v>
       </c>
-      <c r="C8" s="19"/>
+      <c r="C8" s="19" t="s">
+        <v>77</v>
+      </c>
       <c r="D8" s="20" t="s">
         <v>68</v>
       </c>
@@ -2394,22 +2399,27 @@
       <c r="F8" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G8" s="20"/>
+      <c r="G8" s="20">
+        <v>518467776</v>
+      </c>
       <c r="H8" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="21"/>
+      <c r="I8" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K8" s="21">
         <f>M8*12</f>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L8" s="27">
         <f>I8-K8</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M8" s="33">
         <f t="shared" ref="M8:M26" si="0">I8/112</f>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -2421,7 +2431,9 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C9" s="19"/>
+      <c r="C9" s="19" t="s">
+        <v>77</v>
+      </c>
       <c r="D9" s="20" t="s">
         <v>68</v>
       </c>
@@ -2429,22 +2441,27 @@
       <c r="F9" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="20">
+        <v>518467485</v>
+      </c>
       <c r="H9" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="21"/>
+      <c r="I9" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K9" s="21">
         <f t="shared" ref="K9:K26" si="2">M9*12</f>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L9" s="27">
         <f t="shared" ref="L9:L26" si="3">I9-K9</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M9" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -3105,19 +3122,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>1336350.96</v>
+        <v>4009052.88</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>143180.46</v>
+        <v>429541.38</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>1193170.5</v>
+        <v>3579511.5</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>11931.705</v>
+        <v>35795.114999999998</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89279520-0F79-4DED-9C38-BA1C6B391C33}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC51BEE7-B9EB-4BA2-97C5-4D90FE56E29E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="79">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>03/17/2026</t>
+  </si>
+  <si>
+    <t>03/18/2026</t>
   </si>
 </sst>
 </file>
@@ -2473,7 +2476,9 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C10" s="19"/>
+      <c r="C10" s="19" t="s">
+        <v>78</v>
+      </c>
       <c r="D10" s="20" t="s">
         <v>68</v>
       </c>
@@ -2481,22 +2486,27 @@
       <c r="F10" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="20"/>
+      <c r="G10" s="20">
+        <v>518471084</v>
+      </c>
       <c r="H10" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="21"/>
+      <c r="I10" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K10" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L10" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M10" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -2508,7 +2518,9 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C11" s="19"/>
+      <c r="C11" s="19" t="s">
+        <v>78</v>
+      </c>
       <c r="D11" s="20" t="s">
         <v>68</v>
       </c>
@@ -2516,22 +2528,27 @@
       <c r="F11" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="20"/>
+      <c r="G11" s="20">
+        <v>518471366</v>
+      </c>
       <c r="H11" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="21"/>
+      <c r="I11" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K11" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L11" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M11" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -3122,19 +3139,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>4009052.88</v>
+        <v>6681754.7999999998</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>429541.38</v>
+        <v>715902.29999999993</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>3579511.5</v>
+        <v>5965852.5</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>35795.114999999998</v>
+        <v>59658.525000000001</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC51BEE7-B9EB-4BA2-97C5-4D90FE56E29E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00029676-ACE2-4AEE-8808-6DD1C952D330}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="81">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -270,6 +270,12 @@
   </si>
   <si>
     <t>03/18/2026</t>
+  </si>
+  <si>
+    <t>03/20/2026</t>
+  </si>
+  <si>
+    <t>51847------</t>
   </si>
 </sst>
 </file>
@@ -2560,7 +2566,9 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C12" s="19"/>
+      <c r="C12" s="19" t="s">
+        <v>79</v>
+      </c>
       <c r="D12" s="20" t="s">
         <v>68</v>
       </c>
@@ -2568,22 +2576,27 @@
       <c r="F12" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="20"/>
+      <c r="G12" s="20" t="s">
+        <v>80</v>
+      </c>
       <c r="H12" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I12" s="21"/>
+      <c r="I12" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K12" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L12" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M12" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -3139,19 +3152,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>6681754.7999999998</v>
+        <v>8018105.7599999998</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>715902.29999999993</v>
+        <v>859082.75999999989</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>5965852.5</v>
+        <v>7159023</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>59658.525000000001</v>
+        <v>71590.23</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00029676-ACE2-4AEE-8808-6DD1C952D330}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06361CF2-97E6-4EFE-B1DD-ECFBAC54737C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="82">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>51847------</t>
+  </si>
+  <si>
+    <t>03/23/2026</t>
   </si>
 </sst>
 </file>
@@ -2371,7 +2374,7 @@
         <v>74</v>
       </c>
       <c r="I7" s="21">
-        <f>1397196-60845.04</f>
+        <f t="shared" ref="I7:I12" si="0">1397196-60845.04</f>
         <v>1336350.96</v>
       </c>
       <c r="K7" s="21">
@@ -2415,7 +2418,7 @@
         <v>74</v>
       </c>
       <c r="I8" s="21">
-        <f>1397196-60845.04</f>
+        <f t="shared" si="0"/>
         <v>1336350.96</v>
       </c>
       <c r="K8" s="21">
@@ -2427,17 +2430,17 @@
         <v>1193170.5</v>
       </c>
       <c r="M8" s="33">
-        <f t="shared" ref="M8:M26" si="0">I8/112</f>
+        <f t="shared" ref="M8:M26" si="1">I8/112</f>
         <v>11931.705</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <f t="shared" ref="A9:B27" si="1">A8+1</f>
+        <f t="shared" ref="A9:B27" si="2">A8+1</f>
         <v>3</v>
       </c>
       <c r="B9" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="C9" s="19" t="s">
@@ -2457,29 +2460,29 @@
         <v>74</v>
       </c>
       <c r="I9" s="21">
-        <f>1397196-60845.04</f>
+        <f t="shared" si="0"/>
         <v>1336350.96</v>
       </c>
       <c r="K9" s="21">
-        <f t="shared" ref="K9:K26" si="2">M9*12</f>
+        <f t="shared" ref="K9:K26" si="3">M9*12</f>
         <v>143180.46</v>
       </c>
       <c r="L9" s="27">
-        <f t="shared" ref="L9:L26" si="3">I9-K9</f>
+        <f t="shared" ref="L9:L26" si="4">I9-K9</f>
         <v>1193170.5</v>
       </c>
       <c r="M9" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11931.705</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="B10" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="C10" s="19" t="s">
@@ -2499,29 +2502,29 @@
         <v>74</v>
       </c>
       <c r="I10" s="21">
-        <f>1397196-60845.04</f>
+        <f t="shared" si="0"/>
         <v>1336350.96</v>
       </c>
       <c r="K10" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>143180.46</v>
       </c>
       <c r="L10" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1193170.5</v>
       </c>
       <c r="M10" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11931.705</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="B11" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -2541,29 +2544,29 @@
         <v>74</v>
       </c>
       <c r="I11" s="21">
-        <f>1397196-60845.04</f>
+        <f t="shared" si="0"/>
         <v>1336350.96</v>
       </c>
       <c r="K11" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>143180.46</v>
       </c>
       <c r="L11" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1193170.5</v>
       </c>
       <c r="M11" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11931.705</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="B12" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="C12" s="19" t="s">
@@ -2583,32 +2586,34 @@
         <v>74</v>
       </c>
       <c r="I12" s="21">
-        <f>1397196-60845.04</f>
+        <f t="shared" si="0"/>
         <v>1336350.96</v>
       </c>
       <c r="K12" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>143180.46</v>
       </c>
       <c r="L12" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1193170.5</v>
       </c>
       <c r="M12" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11931.705</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="B13" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="C13" s="19"/>
+      <c r="C13" s="19" t="s">
+        <v>81</v>
+      </c>
       <c r="D13" s="20" t="s">
         <v>68</v>
       </c>
@@ -2616,31 +2621,36 @@
       <c r="F13" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G13" s="20"/>
+      <c r="G13" s="20">
+        <v>518484687</v>
+      </c>
       <c r="H13" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I13" s="21"/>
+      <c r="I13" s="21">
+        <f>1377504-85074.83</f>
+        <v>1292429.17</v>
+      </c>
       <c r="K13" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>138474.5539285714</v>
       </c>
       <c r="L13" s="27">
         <f>I13-K13</f>
-        <v>0</v>
+        <v>1153954.6160714286</v>
       </c>
       <c r="M13" s="33">
         <f>I13/112</f>
-        <v>0</v>
+        <v>11539.546160714284</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="B14" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="C14" s="19"/>
@@ -2657,25 +2667,25 @@
       </c>
       <c r="I14" s="38"/>
       <c r="K14" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L14" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M14" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="B15" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="C15" s="19"/>
@@ -2692,7 +2702,7 @@
       </c>
       <c r="I15" s="21"/>
       <c r="K15" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L15" s="27">
@@ -2706,11 +2716,11 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="B16" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="C16" s="19"/>
@@ -2727,25 +2737,25 @@
       </c>
       <c r="I16" s="21"/>
       <c r="K16" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L16" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M16" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="B17" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="C17" s="19"/>
@@ -2762,25 +2772,25 @@
       </c>
       <c r="I17" s="21"/>
       <c r="K17" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L17" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M17" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="B18" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="C18" s="19"/>
@@ -2797,25 +2807,25 @@
       </c>
       <c r="I18" s="21"/>
       <c r="K18" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L18" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M18" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="B19" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="C19" s="19"/>
@@ -2832,25 +2842,25 @@
       </c>
       <c r="I19" s="21"/>
       <c r="K19" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L19" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M19" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="B20" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="C20" s="19"/>
@@ -2867,25 +2877,25 @@
       </c>
       <c r="I20" s="21"/>
       <c r="K20" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L20" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M20" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="B21" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="C21" s="19"/>
@@ -2902,25 +2912,25 @@
       </c>
       <c r="I21" s="21"/>
       <c r="K21" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L21" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M21" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="B22" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="C22" s="19"/>
@@ -2937,25 +2947,25 @@
       </c>
       <c r="I22" s="21"/>
       <c r="K22" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M22" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="B23" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="C23" s="19"/>
@@ -2972,25 +2982,25 @@
       </c>
       <c r="I23" s="21"/>
       <c r="K23" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L23" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M23" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="B24" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="C24" s="19"/>
@@ -3007,25 +3017,25 @@
       </c>
       <c r="I24" s="21"/>
       <c r="K24" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L24" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M24" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="B25" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="C25" s="19"/>
@@ -3042,25 +3052,25 @@
       </c>
       <c r="I25" s="21"/>
       <c r="K25" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L25" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M25" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="B26" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="C26" s="19"/>
@@ -3077,21 +3087,21 @@
       </c>
       <c r="I26" s="21"/>
       <c r="K26" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L26" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M26" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="B27" s="23">
@@ -3112,15 +3122,15 @@
       </c>
       <c r="I27" s="21"/>
       <c r="K27" s="21">
-        <f t="shared" ref="K27" si="4">M27*12</f>
+        <f t="shared" ref="K27" si="5">M27*12</f>
         <v>0</v>
       </c>
       <c r="L27" s="27">
-        <f t="shared" ref="L27" si="5">I27-K27</f>
+        <f t="shared" ref="L27" si="6">I27-K27</f>
         <v>0</v>
       </c>
       <c r="M27" s="33">
-        <f t="shared" ref="M27" si="6">I27/112</f>
+        <f t="shared" ref="M27" si="7">I27/112</f>
         <v>0</v>
       </c>
     </row>
@@ -3152,19 +3162,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>8018105.7599999998</v>
+        <v>9310534.9299999997</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>859082.75999999989</v>
+        <v>997557.3139285713</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>7159023</v>
+        <v>8312977.6160714291</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>71590.23</v>
+        <v>83129.776160714275</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -3289,7 +3299,7 @@
       <c r="H40" s="20"/>
       <c r="I40" s="21"/>
       <c r="K40" s="21">
-        <f t="shared" ref="K40:K59" si="7">M40*12</f>
+        <f t="shared" ref="K40:K59" si="8">M40*12</f>
         <v>0</v>
       </c>
       <c r="L40" s="27">
@@ -3297,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="33">
-        <f t="shared" ref="M40:M59" si="8">I40/112</f>
+        <f t="shared" ref="M40:M59" si="9">I40/112</f>
         <v>0</v>
       </c>
     </row>
@@ -3313,15 +3323,15 @@
       <c r="H41" s="20"/>
       <c r="I41" s="21"/>
       <c r="K41" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L41" s="27">
-        <f t="shared" ref="L41:L59" si="9">I41-K41</f>
+        <f t="shared" ref="L41:L59" si="10">I41-K41</f>
         <v>0</v>
       </c>
       <c r="M41" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -3337,15 +3347,15 @@
       <c r="H42" s="20"/>
       <c r="I42" s="21"/>
       <c r="K42" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L42" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M42" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3361,15 +3371,15 @@
       <c r="H43" s="20"/>
       <c r="I43" s="21"/>
       <c r="K43" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L43" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M43" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3385,15 +3395,15 @@
       <c r="H44" s="20"/>
       <c r="I44" s="21"/>
       <c r="K44" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L44" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M44" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3409,15 +3419,15 @@
       <c r="H45" s="20"/>
       <c r="I45" s="21"/>
       <c r="K45" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L45" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M45" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M45" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3433,15 +3443,15 @@
       <c r="H46" s="20"/>
       <c r="I46" s="21"/>
       <c r="K46" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L46" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M46" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M46" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3457,15 +3467,15 @@
       <c r="H47" s="20"/>
       <c r="I47" s="21"/>
       <c r="K47" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L47" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M47" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M47" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3481,15 +3491,15 @@
       <c r="H48" s="20"/>
       <c r="I48" s="21"/>
       <c r="K48" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L48" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M48" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M48" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3505,15 +3515,15 @@
       <c r="H49" s="20"/>
       <c r="I49" s="21"/>
       <c r="K49" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L49" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M49" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M49" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3529,15 +3539,15 @@
       <c r="H50" s="20"/>
       <c r="I50" s="21"/>
       <c r="K50" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L50" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M50" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3553,15 +3563,15 @@
       <c r="H51" s="20"/>
       <c r="I51" s="21"/>
       <c r="K51" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L51" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M51" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M51" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3577,15 +3587,15 @@
       <c r="H52" s="20"/>
       <c r="I52" s="21"/>
       <c r="K52" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L52" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M52" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M52" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3601,15 +3611,15 @@
       <c r="H53" s="20"/>
       <c r="I53" s="21"/>
       <c r="K53" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L53" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M53" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M53" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3625,15 +3635,15 @@
       <c r="H54" s="20"/>
       <c r="I54" s="21"/>
       <c r="K54" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L54" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M54" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M54" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3649,15 +3659,15 @@
       <c r="H55" s="20"/>
       <c r="I55" s="21"/>
       <c r="K55" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L55" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M55" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M55" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3673,15 +3683,15 @@
       <c r="H56" s="20"/>
       <c r="I56" s="21"/>
       <c r="K56" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L56" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M56" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M56" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3697,15 +3707,15 @@
       <c r="H57" s="20"/>
       <c r="I57" s="21"/>
       <c r="K57" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L57" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M57" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M57" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3721,15 +3731,15 @@
       <c r="H58" s="20"/>
       <c r="I58" s="21"/>
       <c r="K58" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L58" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M58" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3745,15 +3755,15 @@
       <c r="H59" s="20"/>
       <c r="I59" s="21"/>
       <c r="K59" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L59" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M59" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M59" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>

--- a/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06361CF2-97E6-4EFE-B1DD-ECFBAC54737C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D992AAE-1849-4407-8604-6183161B0FAB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="83">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>03/23/2026</t>
+  </si>
+  <si>
+    <t>03/24/2026</t>
   </si>
 </sst>
 </file>
@@ -2653,7 +2656,9 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="C14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>82</v>
+      </c>
       <c r="D14" s="20" t="s">
         <v>68</v>
       </c>
@@ -2661,22 +2666,27 @@
       <c r="F14" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="20"/>
+      <c r="G14" s="20">
+        <v>518489181</v>
+      </c>
       <c r="H14" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="38"/>
+      <c r="I14" s="38">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K14" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L14" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M14" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -2688,7 +2698,9 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="C15" s="19"/>
+      <c r="C15" s="19" t="s">
+        <v>82</v>
+      </c>
       <c r="D15" s="20" t="s">
         <v>68</v>
       </c>
@@ -2696,22 +2708,28 @@
       <c r="F15" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="20"/>
+      <c r="G15" s="20">
+        <f>518488649</f>
+        <v>518488649</v>
+      </c>
       <c r="H15" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I15" s="21"/>
+      <c r="I15" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K15" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L15" s="27">
         <f>I15-K15</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M15" s="33">
         <f>I15/112</f>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -2723,7 +2741,9 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="C16" s="19"/>
+      <c r="C16" s="19" t="s">
+        <v>82</v>
+      </c>
       <c r="D16" s="20" t="s">
         <v>68</v>
       </c>
@@ -2731,22 +2751,27 @@
       <c r="F16" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="20"/>
+      <c r="G16" s="20">
+        <v>518488736</v>
+      </c>
       <c r="H16" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="21"/>
+      <c r="I16" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K16" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L16" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M16" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -3162,19 +3187,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>9310534.9299999997</v>
+        <v>13319587.810000002</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>997557.3139285713</v>
+        <v>1427098.6939285712</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>8312977.6160714291</v>
+        <v>11892489.116071429</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>83129.776160714275</v>
+        <v>118924.89116071428</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D992AAE-1849-4407-8604-6183161B0FAB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EBCC46-6999-43C7-8571-F43F4DDAE0B0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="84">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -282,6 +282,9 @@
   </si>
   <si>
     <t>03/24/2026</t>
+  </si>
+  <si>
+    <t>03/26/2026</t>
   </si>
 </sst>
 </file>
@@ -2783,7 +2786,9 @@
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="C17" s="19"/>
+      <c r="C17" s="19" t="s">
+        <v>83</v>
+      </c>
       <c r="D17" s="20" t="s">
         <v>68</v>
       </c>
@@ -2791,22 +2796,27 @@
       <c r="F17" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="20"/>
+      <c r="G17" s="20">
+        <v>518496823</v>
+      </c>
       <c r="H17" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I17" s="21"/>
+      <c r="I17" s="21">
+        <f>1397196-138903.62</f>
+        <v>1258292.3799999999</v>
+      </c>
       <c r="K17" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>134817.04071428569</v>
       </c>
       <c r="L17" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1123475.3392857141</v>
       </c>
       <c r="M17" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11234.753392857141</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -3187,19 +3197,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>13319587.810000002</v>
+        <v>14577880.190000001</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>1427098.6939285712</v>
+        <v>1561915.7346428568</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>11892489.116071429</v>
+        <v>13015964.455357144</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>118924.89116071428</v>
+        <v>130159.64455357142</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EBCC46-6999-43C7-8571-F43F4DDAE0B0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C328E3-66ED-49FD-89FD-55A520D21EE1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="85">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>03/26/2026</t>
+  </si>
+  <si>
+    <t>03/27/2026</t>
   </si>
 </sst>
 </file>
@@ -2828,7 +2831,9 @@
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="C18" s="19"/>
+      <c r="C18" s="19" t="s">
+        <v>84</v>
+      </c>
       <c r="D18" s="20" t="s">
         <v>68</v>
       </c>
@@ -2836,22 +2841,27 @@
       <c r="F18" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="20"/>
+      <c r="G18" s="20">
+        <v>518501229</v>
+      </c>
       <c r="H18" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="21"/>
+      <c r="I18" s="21">
+        <f>1338600-59929.27</f>
+        <v>1278670.73</v>
+      </c>
       <c r="K18" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>137000.43535714285</v>
       </c>
       <c r="L18" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1141670.294642857</v>
       </c>
       <c r="M18" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11416.702946428572</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -2863,7 +2873,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="C19" s="19"/>
+      <c r="C19" s="19" t="s">
+        <v>84</v>
+      </c>
       <c r="D19" s="20" t="s">
         <v>68</v>
       </c>
@@ -2871,22 +2883,27 @@
       <c r="F19" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="20"/>
+      <c r="G19" s="20">
+        <v>518501527</v>
+      </c>
       <c r="H19" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="21"/>
+      <c r="I19" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K19" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L19" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M19" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -3197,19 +3214,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>14577880.190000001</v>
+        <v>17192901.880000003</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>1561915.7346428568</v>
+        <v>1842096.6299999997</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>13015964.455357144</v>
+        <v>15350805.25</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>130159.64455357142</v>
+        <v>153508.05249999996</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C328E3-66ED-49FD-89FD-55A520D21EE1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EECDA02-5000-4B68-B570-A94D115D1C9F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="86">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -288,6 +288,9 @@
   </si>
   <si>
     <t>03/27/2026</t>
+  </si>
+  <si>
+    <t>03/30/2026</t>
   </si>
 </sst>
 </file>
@@ -2915,7 +2918,9 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="C20" s="19"/>
+      <c r="C20" s="19" t="s">
+        <v>85</v>
+      </c>
       <c r="D20" s="20" t="s">
         <v>68</v>
       </c>
@@ -2923,22 +2928,27 @@
       <c r="F20" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G20" s="20"/>
+      <c r="G20" s="20">
+        <v>518509931</v>
+      </c>
       <c r="H20" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I20" s="21"/>
+      <c r="I20" s="21">
+        <f>1397196-60845.06</f>
+        <v>1336350.94</v>
+      </c>
       <c r="K20" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>143180.45785714284</v>
       </c>
       <c r="L20" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1193170.482142857</v>
       </c>
       <c r="M20" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11931.704821428571</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -3214,19 +3224,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>17192901.880000003</v>
+        <v>18529252.820000004</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>1842096.6299999997</v>
+        <v>1985277.0878571426</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>15350805.25</v>
+        <v>16543975.732142856</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>153508.05249999996</v>
+        <v>165439.75732142854</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/PURCHASES - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EECDA02-5000-4B68-B570-A94D115D1C9F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893174A7-BA42-4A12-9411-66E433E00011}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="87">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>03/30/2026</t>
+  </si>
+  <si>
+    <t>03/31/2026</t>
   </si>
 </sst>
 </file>
@@ -2960,7 +2963,9 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="C21" s="19"/>
+      <c r="C21" s="19" t="s">
+        <v>86</v>
+      </c>
       <c r="D21" s="20" t="s">
         <v>68</v>
       </c>
@@ -2968,22 +2973,27 @@
       <c r="F21" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="20"/>
+      <c r="G21" s="20">
+        <v>518515402</v>
+      </c>
       <c r="H21" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I21" s="21"/>
+      <c r="I21" s="21">
+        <f>1410532-61119.12</f>
+        <v>1349412.88</v>
+      </c>
       <c r="K21" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>144579.95142857142</v>
       </c>
       <c r="L21" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1204832.9285714284</v>
       </c>
       <c r="M21" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12048.329285714284</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -2995,7 +3005,9 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="C22" s="19"/>
+      <c r="C22" s="19" t="s">
+        <v>86</v>
+      </c>
       <c r="D22" s="20" t="s">
         <v>68</v>
       </c>
@@ -3003,22 +3015,27 @@
       <c r="F22" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="20"/>
+      <c r="G22" s="20">
+        <v>518515941</v>
+      </c>
       <c r="H22" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I22" s="21"/>
+      <c r="I22" s="21">
+        <f>1407049-61066.66</f>
+        <v>1345982.34</v>
+      </c>
       <c r="K22" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>144212.39357142858</v>
       </c>
       <c r="L22" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1201769.9464285716</v>
       </c>
       <c r="M22" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12017.699464285715</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -3030,7 +3047,9 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="C23" s="19"/>
+      <c r="C23" s="19" t="s">
+        <v>86</v>
+      </c>
       <c r="D23" s="20" t="s">
         <v>68</v>
       </c>
@@ -3038,22 +3057,27 @@
       <c r="F23" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G23" s="20"/>
+      <c r="G23" s="20">
+        <v>518516276</v>
+      </c>
       <c r="H23" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I23" s="21"/>
+      <c r="I23" s="21">
+        <f>1382580-60763.96</f>
+        <v>1321816.04</v>
+      </c>
       <c r="K23" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>141623.14714285714</v>
       </c>
       <c r="L23" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1180192.892857143</v>
       </c>
       <c r="M23" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11801.928928571429</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -3065,7 +3089,9 @@
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="C24" s="19"/>
+      <c r="C24" s="19" t="s">
+        <v>86</v>
+      </c>
       <c r="D24" s="20" t="s">
         <v>68</v>
       </c>
@@ -3073,22 +3099,27 @@
       <c r="F24" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="20"/>
+      <c r="G24" s="20">
+        <v>518515718</v>
+      </c>
       <c r="H24" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="21"/>
+      <c r="I24" s="21">
+        <f>176525-16425</f>
+        <v>160100</v>
+      </c>
       <c r="K24" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>17153.571428571428</v>
       </c>
       <c r="L24" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>142946.42857142858</v>
       </c>
       <c r="M24" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1429.4642857142858</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -3100,7 +3131,9 @@
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="C25" s="19"/>
+      <c r="C25" s="19" t="s">
+        <v>86</v>
+      </c>
       <c r="D25" s="20" t="s">
         <v>68</v>
       </c>
@@ -3108,22 +3141,27 @@
       <c r="F25" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="20"/>
+      <c r="G25" s="20">
+        <v>518515706</v>
+      </c>
       <c r="H25" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I25" s="21"/>
+      <c r="I25" s="21">
+        <f>347075-14003.02</f>
+        <v>333071.98</v>
+      </c>
       <c r="K25" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>35686.283571428568</v>
       </c>
       <c r="L25" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>297385.69642857142</v>
       </c>
       <c r="M25" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2973.8569642857142</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -3224,19 +3262,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>18529252.820000004</v>
+        <v>23039636.060000002</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>1985277.0878571426</v>
+        <v>2468532.4349999996</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>16543975.732142856</v>
+        <v>20571103.624999996</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>165439.75732142854</v>
+        <v>205711.03624999998</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
